--- a/documents/SADV collections upload test.xlsx
+++ b/documents/SADV collections upload test.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/darryllrobinson/Documents/projects/ciab/documents/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC30787A-64AE-B64F-8B4D-7750C018A076}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA162124-0A55-2D46-9403-FB270D57C764}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="780" yWindow="960" windowWidth="27640" windowHeight="16000" xr2:uid="{B1A7F133-870B-BE4E-A664-D1E75F837A44}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="36">
   <si>
     <t>accountRef</t>
   </si>
@@ -132,6 +132,15 @@
   </si>
   <si>
     <t>Darryll</t>
+  </si>
+  <si>
+    <t>customerRefNo</t>
+  </si>
+  <si>
+    <t>Roelof Terbkans</t>
+  </si>
+  <si>
+    <t>representativeName</t>
   </si>
 </sst>
 </file>
@@ -542,7 +551,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{264374CA-EBDB-1348-8948-C7AE36E6EA27}">
-  <dimension ref="A1:AA2"/>
+  <dimension ref="A1:AC2"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="10.33203125" bestFit="1" customWidth="1"/>
@@ -564,13 +573,14 @@
     <col min="21" max="21" width="3.83203125" bestFit="1" customWidth="1"/>
     <col min="22" max="22" width="9.33203125" bestFit="1" customWidth="1"/>
     <col min="23" max="23" width="12" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="29.33203125" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="4.6640625" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.5" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="9.33203125" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="12" customWidth="1"/>
+    <col min="25" max="25" width="29.33203125" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="4.6640625" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.5" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="9.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:29" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -641,19 +651,25 @@
         <v>22</v>
       </c>
       <c r="X1" t="s">
+        <v>33</v>
+      </c>
+      <c r="Y1" t="s">
         <v>23</v>
       </c>
-      <c r="Y1" t="s">
+      <c r="Z1" t="s">
         <v>24</v>
       </c>
-      <c r="Z1" t="s">
+      <c r="AA1" t="s">
         <v>25</v>
       </c>
-      <c r="AA1" t="s">
+      <c r="AB1" t="s">
+        <v>35</v>
+      </c>
+      <c r="AC1" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="2" spans="1:27" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:29" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>27</v>
       </c>
@@ -696,14 +712,20 @@
       <c r="W2">
         <v>1</v>
       </c>
-      <c r="X2" s="4" t="s">
+      <c r="X2" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="Y2" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="Y2" s="4" t="s">
+      <c r="Z2" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="Z2" s="4" t="s">
+      <c r="AA2" s="4" t="s">
         <v>31</v>
+      </c>
+      <c r="AB2" s="4" t="s">
+        <v>34</v>
       </c>
     </row>
   </sheetData>
